--- a/rmonize/data_proc_elem/DPE_DEGS1_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_DEGS1_P1.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(1=1;2=2;3=3;4=3;5=4;6=6;7=7;8=8)</t>
+          <t>recode(1=1;2=2;3=3;4=3;5=4;6=6;7=7;8=8)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(1=3;2=2;3=1;ELSE=4)</t>
+          <t>recode(1=3;2=2;3=1;ELSE=4)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>mfast + mgsaft</t>
+          <t>mfsaft + mgsaft</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
